--- a/Homepage製作.xlsx
+++ b/Homepage製作.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cs-applemac/CS-MacBook/CSChang/CS－MacBook/龍天宮-20260820/LTG Homepage/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7DDD592-850F-DA47-8CE7-DA59C3F885C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0A9271C7-A039-D146-8A60-2E9E4B883A50}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="5080" yWindow="1820" windowWidth="28240" windowHeight="17320" xr2:uid="{47A2E393-EA9D-BF46-BD21-E709AF4390CF}"/>
+    <workbookView xWindow="19200" yWindow="600" windowWidth="19200" windowHeight="19500" activeTab="1" xr2:uid="{47A2E393-EA9D-BF46-BD21-E709AF4390CF}"/>
   </bookViews>
   <sheets>
     <sheet name="Html" sheetId="1" r:id="rId1"/>
@@ -192,14 +192,14 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>37</xdr:row>
-      <xdr:rowOff>94973</xdr:rowOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>236780</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>342900</xdr:colOff>
+      <xdr:row>29</xdr:row>
+      <xdr:rowOff>331752</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -222,8 +222,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="3810000"/>
-          <a:ext cx="7772400" cy="5924273"/>
+          <a:off x="0" y="4369661"/>
+          <a:ext cx="7704595" cy="5949888"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -322,16 +322,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>88</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>19</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>95</xdr:row>
-      <xdr:rowOff>14808</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>12699</xdr:colOff>
+      <xdr:row>76</xdr:row>
+      <xdr:rowOff>152400</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>30446</xdr:colOff>
+      <xdr:row>86</xdr:row>
+      <xdr:rowOff>63500</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -354,8 +354,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="8255000" y="16764000"/>
-          <a:ext cx="7772400" cy="2415108"/>
+          <a:off x="12699" y="26212800"/>
+          <a:ext cx="10749247" cy="3340100"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -592,10 +592,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>170</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>170180</xdr:colOff>
+      <xdr:row>177</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -619,27 +619,27 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="0" y="54178200"/>
-          <a:ext cx="7772400" cy="4318000"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>171</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>342900</xdr:colOff>
-      <xdr:row>183</xdr:row>
-      <xdr:rowOff>203200</xdr:rowOff>
+          <a:ext cx="11727180" cy="6515100"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>12700</xdr:colOff>
+      <xdr:row>176</xdr:row>
+      <xdr:rowOff>76200</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>355600</xdr:colOff>
+      <xdr:row>188</xdr:row>
+      <xdr:rowOff>279400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -662,7 +662,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="0" y="58635900"/>
+          <a:off x="12700" y="60426600"/>
           <a:ext cx="7772400" cy="4318000"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
